--- a/output/Data and Chart Outputs/bangladesh_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/bangladesh_power_capacity.xlsx
@@ -157,6 +157,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Bangladesh installed capacity (BPDB) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -290,7 +291,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -318,7 +319,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="8A9A2B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -346,7 +347,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -374,7 +375,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E34948"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>

--- a/output/Data and Chart Outputs/bangladesh_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/bangladesh_power_capacity.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,12 +63,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -827,7 +828,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -842,7 +842,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -922,7 +921,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>46296</v>
       </c>
       <c r="B2" t="n">
